--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityBusinessDetails001.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityBusinessDetails001.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CS\code\XXPL\tams-svreport\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11760"/>
   </bookViews>
@@ -12,10 +17,17 @@
     <sheet name="版本号1.0.0" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="asd">填写说明!$A$7:$A$46</definedName>
     <definedName name="bz">填写说明!$A$143:$A$320</definedName>
+    <definedName name="cvb">填写说明!$A$51:$A$87</definedName>
+    <definedName name="fgh">填写说明!$A$106:$A$141</definedName>
     <definedName name="gmd">填写说明!$A$7:$A$46</definedName>
     <definedName name="qd">填写说明!$A$323:$A$329</definedName>
+    <definedName name="qwe">填写说明!$A$106:$A$141</definedName>
+    <definedName name="qwqe">填写说明!$A$106:$A$141</definedName>
+    <definedName name="rty">填写说明!$A$106:$A$141</definedName>
     <definedName name="ywzl">填写说明!$A$89:$A$104</definedName>
+    <definedName name="zxc">填写说明!$A$48:$A$49</definedName>
     <definedName name="关联账户所在地">填写说明!$A$7:$A$46</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
@@ -1371,6 +1383,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1723,7 +1738,8 @@
     <col min="26" max="26" width="16.875" style="28" customWidth="1" collapsed="1"/>
     <col min="27" max="27" width="17.375" style="28" customWidth="1" collapsed="1"/>
     <col min="28" max="28" width="9" style="29" collapsed="1"/>
-    <col min="29" max="30" width="9" style="29"/>
+    <col min="29" max="29" width="9" style="29"/>
+    <col min="30" max="30" width="0" style="29" hidden="1" customWidth="1"/>
     <col min="31" max="16384" width="9" style="29" collapsed="1"/>
   </cols>
   <sheetData>
@@ -1812,8 +1828,11 @@
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
-  <dataValidations count="4">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:J1 M1 O1:P1 S1 Y1"/>
+  <dataValidations count="9">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y1 S1 O1"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q4">
+      <formula1>qwe</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576">
       <formula1>bz</formula1>
     </dataValidation>
@@ -1823,39 +1842,21 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y1048576">
       <formula1>qd</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I1048576">
+      <formula1>asd</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J1048576">
+      <formula1>zxc</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M1048576">
+      <formula1>cvb</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2 P3:P1048576">
+      <formula1>fgh</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555596" footer="0.51180555555555596"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>填写说明!$A$7:$A$46</xm:f>
-          </x14:formula1>
-          <xm:sqref>I2:I1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>填写说明!$A$48:$A$49</xm:f>
-          </x14:formula1>
-          <xm:sqref>J2:J1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>填写说明!$A$51:$A$87</xm:f>
-          </x14:formula1>
-          <xm:sqref>M2:M1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>填写说明!$A$106:$A$141</xm:f>
-          </x14:formula1>
-          <xm:sqref>P2:P1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
@@ -1867,30 +1868,30 @@
     <col min="1" max="1" width="73.375" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" ht="15.75">
       <c r="A1" s="6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="28.5">
+    <row r="2" spans="1:1" ht="30">
       <c r="A2" s="7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" ht="15.75">
       <c r="A3" s="8" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" ht="15.75">
       <c r="A4" s="9" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" ht="15.75">
       <c r="A5" s="10"/>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" ht="15.75">
       <c r="A6" s="11" t="s">
         <v>36</v>
       </c>
